--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230201_20230801.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230201_20230801.xlsx
@@ -833,37 +833,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.85123966942148</v>
+        <v>58.67768595041323</v>
       </c>
       <c r="C10" t="n">
-        <v>41.32231404958678</v>
+        <v>39.66942148760331</v>
       </c>
       <c r="D10" t="n">
-        <v>134.3708930196084</v>
+        <v>77.15089770249197</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>INE324A01032</t>
+          <t>INE242C01024</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>-16.5289256198347</v>
+        <v>-19.00826446280992</v>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
         <v>46</v>
       </c>
       <c r="J10" t="n">
-        <v>162.2</v>
+        <v>201.65</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
@@ -877,37 +877,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.67768595041323</v>
+        <v>57.85123966942148</v>
       </c>
       <c r="C11" t="n">
-        <v>39.66942148760331</v>
+        <v>41.32231404958678</v>
       </c>
       <c r="D11" t="n">
-        <v>77.15089770249197</v>
+        <v>134.3708930196084</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>INE242C01024</t>
+          <t>INE324A01032</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>-19.00826446280992</v>
+        <v>-16.5289256198347</v>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="I11" t="n">
         <v>46</v>
       </c>
       <c r="J11" t="n">
-        <v>201.65</v>
+        <v>162.2</v>
       </c>
       <c r="K11" t="n">
         <v>10</v>
